--- a/outputs/208-20.xlsx
+++ b/outputs/208-20.xlsx
@@ -327,131 +327,131 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="2" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="4" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="11" fillId="0" borderId="4" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="5" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="7" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="11" fillId="0" borderId="7" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="8" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="10" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="11" fillId="0" borderId="10" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="11" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="12" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -756,7 +756,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N37"/>
-  <sheetFormatPr defaultColWidth="11.88671875" defaultRowHeight="19.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.89453125" defaultRowHeight="19.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="8.88"/>
@@ -837,7 +837,7 @@
       </c>
       <c r="E3" s="18"/>
       <c r="F3" s="19" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E23)),A23,"")</f>
+        <f aca="false">IF(NOT(ISBLANK(E3)),A3,"")</f>
         <v/>
       </c>
       <c r="I3" s="14" t="s">
@@ -870,7 +870,7 @@
       </c>
       <c r="E4" s="24"/>
       <c r="F4" s="25" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E24)),A24,"")</f>
+        <f aca="false">IF(NOT(ISBLANK(E4)),A4,"")</f>
         <v/>
       </c>
       <c r="I4" s="20" t="s">
@@ -903,7 +903,7 @@
       </c>
       <c r="E5" s="24"/>
       <c r="F5" s="25" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E25)),A25,"")</f>
+        <f aca="false">IF(NOT(ISBLANK(E5)),A5,"")</f>
         <v/>
       </c>
       <c r="I5" s="20" t="s">
@@ -936,7 +936,7 @@
       </c>
       <c r="E6" s="24"/>
       <c r="F6" s="25" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E26)),A26,"")</f>
+        <f aca="false">IF(NOT(ISBLANK(E6)),A6,"")</f>
         <v/>
       </c>
       <c r="I6" s="20" t="s">
@@ -971,8 +971,8 @@
         <v>15</v>
       </c>
       <c r="F7" s="31" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E27)),A27,"")</f>
-        <v>SUNPHARMA.NS</v>
+        <f aca="false">IF(NOT(ISBLANK(E7)),A7,"")</f>
+        <v>UPL.NS</v>
       </c>
       <c r="I7" s="26" t="s">
         <v>6</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="E8" s="18"/>
       <c r="F8" s="19" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E28)),A28,"")</f>
+        <f aca="false">IF(NOT(ISBLANK(E8)),A8,"")</f>
         <v/>
       </c>
       <c r="I8" s="14" t="s">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="E9" s="24"/>
       <c r="F9" s="25" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E29)),A29,"")</f>
+        <f aca="false">IF(NOT(ISBLANK(E9)),A9,"")</f>
         <v/>
       </c>
       <c r="I9" s="20" t="s">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E10" s="24"/>
       <c r="F10" s="25" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E30)),A30,"")</f>
+        <f aca="false">IF(NOT(ISBLANK(E10)),A10,"")</f>
         <v/>
       </c>
       <c r="I10" s="20" t="s">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="E11" s="24"/>
       <c r="F11" s="25" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E31)),A31,"")</f>
+        <f aca="false">IF(NOT(ISBLANK(E11)),A11,"")</f>
         <v/>
       </c>
       <c r="I11" s="20" t="s">
@@ -1141,9 +1141,9 @@
       <c r="E12" s="30" t="n">
         <v>15</v>
       </c>
-      <c r="F12" s="32" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E32)),A32,"")</f>
-        <v>TCS.NS</v>
+      <c r="F12" s="31" t="str">
+        <f aca="false">IF(NOT(ISBLANK(E12)),A12,"")</f>
+        <v>AXISBANK.NS</v>
       </c>
       <c r="I12" s="26" t="s">
         <v>8</v>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="E13" s="18"/>
       <c r="F13" s="19" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E3)),A3,"")</f>
+        <f aca="false">IF(NOT(ISBLANK(E13)),A13,"")</f>
         <v/>
       </c>
       <c r="I13" s="14" t="s">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="E14" s="24"/>
       <c r="F14" s="25" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E4)),A4,"")</f>
+        <f aca="false">IF(NOT(ISBLANK(E14)),A14,"")</f>
         <v/>
       </c>
       <c r="I14" s="20" t="s">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="E15" s="24"/>
       <c r="F15" s="25" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E5)),A5,"")</f>
+        <f aca="false">IF(NOT(ISBLANK(E15)),A15,"")</f>
         <v/>
       </c>
       <c r="I15" s="20" t="s">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="E16" s="24"/>
       <c r="F16" s="25" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E6)),A6,"")</f>
+        <f aca="false">IF(NOT(ISBLANK(E16)),A16,"")</f>
         <v/>
       </c>
       <c r="I16" s="20" t="s">
@@ -1313,8 +1313,8 @@
         <v>7</v>
       </c>
       <c r="F17" s="31" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E7)),A7,"")</f>
-        <v>UPL.NS</v>
+        <f aca="false">IF(NOT(ISBLANK(E17)),A17,"")</f>
+        <v>^NSEI</v>
       </c>
       <c r="I17" s="26" t="s">
         <v>9</v>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="E18" s="18"/>
       <c r="F18" s="19" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E33)),A33,"")</f>
+        <f aca="false">IF(NOT(ISBLANK(E18)),A18,"")</f>
         <v/>
       </c>
       <c r="I18" s="14" t="s">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="E19" s="24"/>
       <c r="F19" s="25" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E34)),A34,"")</f>
+        <f aca="false">IF(NOT(ISBLANK(E19)),A19,"")</f>
         <v/>
       </c>
       <c r="I19" s="20" t="s">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="E20" s="24"/>
       <c r="F20" s="25" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E35)),A35,"")</f>
+        <f aca="false">IF(NOT(ISBLANK(E20)),A20,"")</f>
         <v/>
       </c>
       <c r="I20" s="20" t="s">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="E21" s="24"/>
       <c r="F21" s="25" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E36)),A36,"")</f>
+        <f aca="false">IF(NOT(ISBLANK(E21)),A21,"")</f>
         <v/>
       </c>
       <c r="I21" s="20" t="s">
@@ -1484,8 +1484,8 @@
         <v>4</v>
       </c>
       <c r="F22" s="31" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E37)),A37,"")</f>
-        <v>LT.NS</v>
+        <f aca="false">IF(NOT(ISBLANK(E22)),A22,"")</f>
+        <v>JUBLFOOD.NS</v>
       </c>
       <c r="I22" s="26" t="s">
         <v>11</v>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="E23" s="18"/>
       <c r="F23" s="19" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E18)),A18,"")</f>
+        <f aca="false">IF(NOT(ISBLANK(E23)),A23,"")</f>
         <v/>
       </c>
       <c r="I23" s="14" t="s">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="E24" s="24"/>
       <c r="F24" s="25" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E19)),A19,"")</f>
+        <f aca="false">IF(NOT(ISBLANK(E24)),A24,"")</f>
         <v/>
       </c>
       <c r="I24" s="20" t="s">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="E25" s="24"/>
       <c r="F25" s="25" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E20)),A20,"")</f>
+        <f aca="false">IF(NOT(ISBLANK(E25)),A25,"")</f>
         <v/>
       </c>
       <c r="I25" s="20" t="s">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="E26" s="24"/>
       <c r="F26" s="25" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E21)),A21,"")</f>
+        <f aca="false">IF(NOT(ISBLANK(E26)),A26,"")</f>
         <v/>
       </c>
       <c r="I26" s="20" t="s">
@@ -1655,8 +1655,8 @@
         <v>3</v>
       </c>
       <c r="F27" s="31" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E22)),A22,"")</f>
-        <v>JUBLFOOD.NS</v>
+        <f aca="false">IF(NOT(ISBLANK(E27)),A27,"")</f>
+        <v>SUNPHARMA.NS</v>
       </c>
       <c r="I27" s="26" t="s">
         <v>12</v>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="E28" s="18"/>
       <c r="F28" s="19" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E8)),A8,"")</f>
+        <f aca="false">IF(NOT(ISBLANK(E28)),A28,"")</f>
         <v/>
       </c>
       <c r="I28" s="14" t="s">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="E29" s="24"/>
       <c r="F29" s="25" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E9)),A9,"")</f>
+        <f aca="false">IF(NOT(ISBLANK(E29)),A29,"")</f>
         <v/>
       </c>
       <c r="I29" s="20" t="s">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="E30" s="24"/>
       <c r="F30" s="25" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E10)),A10,"")</f>
+        <f aca="false">IF(NOT(ISBLANK(E30)),A30,"")</f>
         <v/>
       </c>
       <c r="I30" s="20" t="s">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="E31" s="24"/>
       <c r="F31" s="25" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E11)),A11,"")</f>
+        <f aca="false">IF(NOT(ISBLANK(E31)),A31,"")</f>
         <v/>
       </c>
       <c r="I31" s="20" t="s">
@@ -1825,9 +1825,9 @@
       <c r="E32" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="F32" s="31" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E12)),A12,"")</f>
-        <v>AXISBANK.NS</v>
+      <c r="F32" s="32" t="str">
+        <f aca="false">IF(NOT(ISBLANK(E32)),A32,"")</f>
+        <v>TCS.NS</v>
       </c>
       <c r="I32" s="26" t="s">
         <v>13</v>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E33" s="18"/>
       <c r="F33" s="19" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E13)),A13,"")</f>
+        <f aca="false">IF(NOT(ISBLANK(E33)),A33,"")</f>
         <v/>
       </c>
       <c r="I33" s="14" t="s">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="E34" s="24"/>
       <c r="F34" s="25" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E14)),A14,"")</f>
+        <f aca="false">IF(NOT(ISBLANK(E34)),A34,"")</f>
         <v/>
       </c>
       <c r="I34" s="20" t="s">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="E35" s="24"/>
       <c r="F35" s="25" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E15)),A15,"")</f>
+        <f aca="false">IF(NOT(ISBLANK(E35)),A35,"")</f>
         <v/>
       </c>
       <c r="I35" s="20" t="s">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="E36" s="24"/>
       <c r="F36" s="25" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E16)),A16,"")</f>
+        <f aca="false">IF(NOT(ISBLANK(E36)),A36,"")</f>
         <v/>
       </c>
       <c r="I36" s="20" t="s">
@@ -1997,8 +1997,8 @@
         <v>2</v>
       </c>
       <c r="F37" s="31" t="str">
-        <f aca="false">IF(NOT(ISBLANK(E17)),A17,"")</f>
-        <v>^NSEI</v>
+        <f aca="false">IF(NOT(ISBLANK(E37)),A37,"")</f>
+        <v>LT.NS</v>
       </c>
       <c r="I37" s="26" t="s">
         <v>14</v>
